--- a/outputs/monitor_xlsx/20260309.xlsx
+++ b/outputs/monitor_xlsx/20260309.xlsx
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2364,7 +2364,7 @@
         <v>-106287</v>
       </c>
       <c r="N23" t="n">
-        <v>6.06</v>
+        <v>1.38</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -2422,6 +2422,59 @@
       <c r="O24" t="inlineStr">
         <is>
           <t>偏多</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4980</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-5.14</v>
+      </c>
+      <c r="E25" t="n">
+        <v>806</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>-206</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-52</v>
+      </c>
+      <c r="H25" t="n">
+        <v>73</v>
+      </c>
+      <c r="I25" t="n">
+        <v>191</v>
+      </c>
+      <c r="J25" t="n">
+        <v>43</v>
+      </c>
+      <c r="K25" t="n">
+        <v>242</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1484</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-8938</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260309.xlsx
+++ b/outputs/monitor_xlsx/20260309.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -526,220 +526,232 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>美債10年殖利率</t>
+          <t>加權指數 (TWII)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.14%</t>
+          <t>32110.42</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+0.17%</t>
-        </is>
-      </c>
+          <t>-4.43%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>黃金指數 (GC=F)</t>
+          <t>櫃買指數 (OTC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5146.7$</t>
+          <t>288.96</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
+          <t>-5.72%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>貨幣</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>美元/台幣匯率</t>
+          <t>台指近月期貨</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.8</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>現貨</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>費半指數 (SOX)</t>
+          <t>美債10年殖利率</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7810.4</t>
+          <t>4.14%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+3.93%</t>
-        </is>
-      </c>
+          <t>+0.17%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>情緒</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>恐慌指數 (VIX)</t>
+          <t>黃金指數 (GC=F)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>5091.5$</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-13.53%</t>
-        </is>
-      </c>
+          <t>-1.06%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>原物料</t>
+          <t>貨幣</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WTI原油期貨</t>
+          <t>美元/台幣匯率</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>85.72$</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-5.70%</t>
-        </is>
-      </c>
+          <t>-0.33%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>現貨</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>外資現貨</t>
+          <t>費半指數 (SOX)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1208.17億</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>-797.74億</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-3988.72億</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-174.25億</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-3484.95億</t>
-        </is>
-      </c>
+          <t>7810.4</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>+3.93%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>情緒</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>投信現貨</t>
+          <t>恐慌指數 (VIX)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>135.71億</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>91.7億</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>458.48億</t>
-        </is>
-      </c>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-13.53%</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>原物料</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>選擇權 P/C Ratio</t>
+          <t>WTI原油期貨</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>101.18%</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>125.42%</t>
-        </is>
-      </c>
+          <t>94.77$</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>+4.26%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -749,12 +761,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>三大法人合計</t>
+          <t>外資現貨</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1658.85億</t>
+          <t>-1208.17億</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-797.74億</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-3988.72億</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-174.25億</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-3484.95億</t>
         </is>
       </c>
     </row>
@@ -766,54 +799,137 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>外資期貨未平倉</t>
+          <t>投信現貨</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20634口</t>
-        </is>
-      </c>
+          <t>135.71億</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19007口</t>
-        </is>
-      </c>
+          <t>91.7億</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>458.48億</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>選擇權 P/C Ratio</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>141.14%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>None%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>三大法人合計</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-1658.85億</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>外資期貨未平倉</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>20634口</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>19007口</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>結算</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>融資融券變化</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>96.54億</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>31.93億</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>159.64億</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0.12億</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2.38億</t>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>33.72億</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>168.58億</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>None億</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -900,6 +1016,10 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -939,7 +1059,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>31.93億</t>
+          <t>33.72億</t>
         </is>
       </c>
     </row>
@@ -951,7 +1071,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>159.64億</t>
+          <t>168.58億</t>
         </is>
       </c>
     </row>
@@ -963,7 +1083,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.12億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -975,7 +1095,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2.38億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -994,7 +1114,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>125.42%</t>
+          <t>None%</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1039,14 +1159,13 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1056,7 +1175,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1135,40 +1253,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1203,13 +1316,13 @@
         <v>-200178</v>
       </c>
       <c r="H4" t="n">
-        <v>-525063</v>
+        <v>-423563</v>
       </c>
       <c r="I4" t="n">
         <v>4948</v>
       </c>
       <c r="J4" t="n">
-        <v>14086</v>
+        <v>10872</v>
       </c>
       <c r="K4" t="n">
         <v>220371</v>
@@ -1218,20 +1331,12 @@
         <v>14387</v>
       </c>
       <c r="M4" t="n">
-        <v>51145</v>
+        <v>43522</v>
       </c>
       <c r="N4" t="n">
         <v>-4389094</v>
       </c>
-      <c r="O4" t="n">
-        <v>-5.39</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1240,41 +1345,53 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00708L</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S&amp;P黃金正2</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>64</v>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>871</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>-5.94</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4645</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>-3</v>
       </c>
       <c r="H5" t="n">
-        <v>-1232</v>
+        <v>-1795</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-354</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-233</v>
       </c>
       <c r="K5" t="n">
-        <v>752</v>
+        <v>365</v>
       </c>
       <c r="L5" t="n">
-        <v>9670</v>
+        <v>2768</v>
       </c>
       <c r="M5" t="n">
-        <v>49918</v>
+        <v>11314</v>
       </c>
       <c r="N5" t="n">
-        <v>-27173</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+        <v>-78828</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1283,12 +1400,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1297,47 +1414,39 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>871</v>
+        <v>1220</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>-5.94</v>
+        <v>-7.58</v>
       </c>
       <c r="F6" t="n">
-        <v>4645</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>-3</v>
+        <v>23398</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>654</v>
       </c>
       <c r="H6" t="n">
-        <v>-2518</v>
+        <v>-5468</v>
       </c>
       <c r="I6" t="n">
-        <v>-354</v>
+        <v>267</v>
       </c>
       <c r="J6" t="n">
-        <v>-194</v>
+        <v>1054</v>
       </c>
       <c r="K6" t="n">
-        <v>365</v>
+        <v>4578</v>
       </c>
       <c r="L6" t="n">
-        <v>2768</v>
+        <v>5777</v>
       </c>
       <c r="M6" t="n">
-        <v>14267</v>
+        <v>22763</v>
       </c>
       <c r="N6" t="n">
-        <v>-78828</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-9.27</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+        <v>-649014</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1346,12 +1455,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1360,47 +1469,39 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1220</v>
+        <v>1810</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>-7.58</v>
+        <v>-4.23</v>
       </c>
       <c r="F7" t="n">
-        <v>23398</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>654</v>
+        <v>94441</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>-37837</v>
       </c>
       <c r="H7" t="n">
-        <v>-5258</v>
+        <v>-69233</v>
       </c>
       <c r="I7" t="n">
-        <v>267</v>
+        <v>2661</v>
       </c>
       <c r="J7" t="n">
-        <v>1217</v>
+        <v>5185</v>
       </c>
       <c r="K7" t="n">
-        <v>4578</v>
+        <v>8007</v>
       </c>
       <c r="L7" t="n">
-        <v>5777</v>
+        <v>25279</v>
       </c>
       <c r="M7" t="n">
-        <v>29393</v>
+        <v>92535</v>
       </c>
       <c r="N7" t="n">
-        <v>-649014</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-8.609999999999999</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+        <v>-6482931</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1409,12 +1510,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1423,47 +1524,39 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1810</v>
+        <v>1380</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-4.23</v>
+        <v>-5.8</v>
       </c>
       <c r="F8" t="n">
-        <v>94441</v>
+        <v>5813</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>-37837</v>
+        <v>-784</v>
       </c>
       <c r="H8" t="n">
-        <v>-88771</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>2661</v>
+        <v>167</v>
       </c>
       <c r="J8" t="n">
-        <v>7809</v>
+        <v>173</v>
       </c>
       <c r="K8" t="n">
-        <v>8007</v>
+        <v>284</v>
       </c>
       <c r="L8" t="n">
-        <v>25279</v>
+        <v>1808</v>
       </c>
       <c r="M8" t="n">
-        <v>113748</v>
+        <v>8108</v>
       </c>
       <c r="N8" t="n">
-        <v>-6482931</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-5.38</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+        <v>-140179</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1472,12 +1565,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1486,47 +1579,39 @@
         </is>
       </c>
       <c r="D9" t="n">
+        <v>1240</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-9.82</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3029</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>-231</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-1773</v>
+      </c>
+      <c r="I9" t="n">
+        <v>40</v>
+      </c>
+      <c r="J9" t="n">
+        <v>402</v>
+      </c>
+      <c r="K9" t="n">
         <v>101</v>
       </c>
-      <c r="E9" s="6" t="n">
-        <v>-5.16</v>
-      </c>
-      <c r="F9" t="n">
-        <v>168056</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>22001</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1705</v>
-      </c>
-      <c r="I9" t="n">
-        <v>50</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-5719</v>
-      </c>
-      <c r="K9" t="n">
-        <v>9102</v>
-      </c>
       <c r="L9" t="n">
-        <v>116881</v>
+        <v>3283</v>
       </c>
       <c r="M9" t="n">
-        <v>642869</v>
+        <v>11534</v>
       </c>
       <c r="N9" t="n">
-        <v>-1114030</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-9.74</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+        <v>-106287</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1561,13 +1646,13 @@
         <v>-327</v>
       </c>
       <c r="H10" t="n">
-        <v>-1205</v>
+        <v>-1387</v>
       </c>
       <c r="I10" t="n">
         <v>173</v>
       </c>
       <c r="J10" t="n">
-        <v>1019</v>
+        <v>917</v>
       </c>
       <c r="K10" t="n">
         <v>194</v>
@@ -1576,20 +1661,12 @@
         <v>1754</v>
       </c>
       <c r="M10" t="n">
-        <v>9271</v>
+        <v>7315</v>
       </c>
       <c r="N10" t="n">
         <v>-89500</v>
       </c>
-      <c r="O10" t="n">
-        <v>-6.37</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1598,12 +1675,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1612,47 +1689,39 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2995</v>
+        <v>1710</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>-9.52</v>
+        <v>-9.76</v>
       </c>
       <c r="F11" t="n">
-        <v>2382</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>-854</v>
+        <v>221</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>29</v>
       </c>
       <c r="H11" t="n">
-        <v>-466</v>
+        <v>220</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="J11" t="n">
-        <v>166</v>
+        <v>202</v>
       </c>
       <c r="K11" t="n">
-        <v>303</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>5967</v>
+        <v>4641</v>
       </c>
       <c r="M11" t="n">
-        <v>29681</v>
+        <v>17440</v>
       </c>
       <c r="N11" t="n">
-        <v>-19736</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-9.210000000000001</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+        <v>-19186</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1661,12 +1730,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1675,47 +1744,39 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1710</v>
+        <v>4980</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>-9.76</v>
+        <v>-5.14</v>
       </c>
       <c r="F12" t="n">
-        <v>221</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>29</v>
+        <v>806</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>-206</v>
       </c>
       <c r="H12" t="n">
-        <v>-388</v>
+        <v>154</v>
       </c>
       <c r="I12" t="n">
-        <v>-1</v>
+        <v>73</v>
       </c>
       <c r="J12" t="n">
-        <v>792</v>
+        <v>118</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="L12" t="n">
-        <v>4641</v>
+        <v>242</v>
       </c>
       <c r="M12" t="n">
-        <v>22480</v>
+        <v>1228</v>
       </c>
       <c r="N12" t="n">
-        <v>-19186</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-19.83</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+        <v>-8938</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1738,25 +1799,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1350</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>-10</v>
+        <v>2315</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>9.98</v>
       </c>
       <c r="F13" t="n">
-        <v>2988</v>
+        <v>2730</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>-677</v>
       </c>
       <c r="H13" t="n">
-        <v>-1305</v>
+        <v>-1437</v>
       </c>
       <c r="I13" t="n">
         <v>256</v>
       </c>
       <c r="J13" t="n">
-        <v>1444</v>
+        <v>1301</v>
       </c>
       <c r="K13" t="n">
         <v>-38</v>
@@ -1765,20 +1826,12 @@
         <v>-14</v>
       </c>
       <c r="M13" t="n">
-        <v>-59</v>
+        <v>-181</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1787,12 +1840,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>台新科</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1801,44 +1854,39 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>124.5</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>-9.779999999999999</v>
+        <v>449.5</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>4.78</v>
       </c>
       <c r="F14" t="n">
-        <v>1643</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>-445</v>
+        <v>3871</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>20</v>
       </c>
       <c r="H14" t="n">
-        <v>66</v>
+        <v>608</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0</v>
       </c>
       <c r="J14" t="n">
-        <v>-1</v>
+        <v>-2164</v>
       </c>
       <c r="K14" t="n">
-        <v>-131</v>
+        <v>-114</v>
       </c>
       <c r="L14" t="n">
-        <v>57</v>
+        <v>-303</v>
       </c>
       <c r="M14" t="n">
-        <v>-122</v>
+        <v>-453</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1847,12 +1895,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1861,47 +1909,36 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>341.5</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>-9.890000000000001</v>
+        <v>974</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>9.93</v>
       </c>
       <c r="F15" t="n">
-        <v>1424</v>
+        <v>1350</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="H15" t="n">
-        <v>1571</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
+        <v>2467</v>
       </c>
       <c r="J15" t="n">
-        <v>-985</v>
+        <v>307</v>
       </c>
       <c r="K15" t="n">
-        <v>-114</v>
+        <v>-95</v>
       </c>
       <c r="L15" t="n">
-        <v>-303</v>
+        <v>-191</v>
       </c>
       <c r="M15" t="n">
-        <v>-775</v>
+        <v>-138</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1910,12 +1947,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1924,557 +1961,41 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1180</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>-9.92</v>
+        <v>1600</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>4.92</v>
       </c>
       <c r="F16" t="n">
-        <v>440</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>52</v>
+        <v>904</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>-116</v>
       </c>
       <c r="H16" t="n">
-        <v>-1082</v>
+        <v>333</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="K16" t="n">
-        <v>-21</v>
+        <v>-53</v>
       </c>
       <c r="L16" t="n">
-        <v>-80</v>
+        <v>-4</v>
       </c>
       <c r="M16" t="n">
-        <v>338</v>
+        <v>16</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>3138</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>耀登</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>162.5</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>-9.970000000000001</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1059</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>-16</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-184</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3</v>
-      </c>
-      <c r="L17" t="n">
-        <v>4134</v>
-      </c>
-      <c r="M17" t="n">
-        <v>23342</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-11595</v>
-      </c>
-      <c r="O17" t="n">
-        <v>-18.18</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1380</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>-5.8</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>5813</v>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>-784</v>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>-781</v>
-      </c>
-      <c r="H18" t="n">
-        <v>167</v>
-      </c>
-      <c r="I18" t="n">
-        <v>340</v>
-      </c>
-      <c r="J18" t="n">
-        <v>284</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1808</v>
-      </c>
-      <c r="L18" t="n">
-        <v>9229</v>
-      </c>
-      <c r="M18" t="n">
-        <v>-140179</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>3163</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>波若威</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>651</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>-9.960000000000001</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1241</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>106</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1022</v>
-      </c>
-      <c r="J19" t="n">
-        <v>20</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L19" t="n">
-        <v>-249</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-570</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>漢唐</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1070</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>-2.73</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>3676</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>-265</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>1089</v>
-      </c>
-      <c r="H20" t="n">
-        <v>493</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1346</v>
-      </c>
-      <c r="J20" t="n">
-        <v>302</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1972</v>
-      </c>
-      <c r="L20" t="n">
-        <v>10312</v>
-      </c>
-      <c r="M20" t="n">
-        <v>-47591</v>
-      </c>
-      <c r="N20" t="n">
-        <v>8.76</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>6640</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>均華</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>962</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E21" t="n">
-        <v>826</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>-116</v>
-      </c>
-      <c r="G21" t="n">
-        <v>217</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>16</v>
-      </c>
-      <c r="J21" t="n">
-        <v>-53</v>
-      </c>
-      <c r="K21" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L21" t="n">
-        <v>12</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>624</v>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2040</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>82</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2549</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>307</v>
-      </c>
-      <c r="J22" t="n">
-        <v>-95</v>
-      </c>
-      <c r="K22" t="n">
-        <v>-191</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-329</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1240</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>-9.82</v>
-      </c>
-      <c r="E23" t="n">
-        <v>3029</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>-231</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-2004</v>
-      </c>
-      <c r="H23" t="n">
-        <v>40</v>
-      </c>
-      <c r="I23" t="n">
-        <v>442</v>
-      </c>
-      <c r="J23" t="n">
-        <v>101</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3283</v>
-      </c>
-      <c r="L23" t="n">
-        <v>14568</v>
-      </c>
-      <c r="M23" t="n">
-        <v>-106287</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>3030</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>德律</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>231.5</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>-5.51</v>
-      </c>
-      <c r="E24" t="n">
-        <v>6359</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>1145</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1281</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>477</v>
-      </c>
-      <c r="J24" t="n">
-        <v>415</v>
-      </c>
-      <c r="K24" t="n">
-        <v>6738</v>
-      </c>
-      <c r="L24" t="n">
-        <v>34458</v>
-      </c>
-      <c r="M24" t="n">
-        <v>-58901</v>
-      </c>
-      <c r="N24" t="n">
-        <v>12.62</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>4980</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>-5.14</v>
-      </c>
-      <c r="E25" t="n">
-        <v>806</v>
-      </c>
-      <c r="F25" s="7" t="n">
-        <v>-206</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-52</v>
-      </c>
-      <c r="H25" t="n">
-        <v>73</v>
-      </c>
-      <c r="I25" t="n">
-        <v>191</v>
-      </c>
-      <c r="J25" t="n">
-        <v>43</v>
-      </c>
-      <c r="K25" t="n">
-        <v>242</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1484</v>
-      </c>
-      <c r="M25" t="n">
-        <v>-8938</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260309.xlsx
+++ b/outputs/monitor_xlsx/20260309.xlsx
@@ -544,10 +544,6 @@
           <t>-4.43%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>-5.72%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -591,11 +583,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -618,10 +605,6 @@
           <t>+0.17%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -644,10 +627,6 @@
           <t>-1.06%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -670,10 +649,6 @@
           <t>-0.33%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -696,10 +671,6 @@
           <t>+3.93%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -722,10 +693,6 @@
           <t>-13.53%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -748,10 +715,6 @@
           <t>+4.26%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -769,7 +732,6 @@
           <t>-1208.17億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-797.74億</t>
@@ -807,7 +769,6 @@
           <t>135.71億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>91.7億</t>
@@ -818,8 +779,6 @@
           <t>458.48億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,15 +796,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>None%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -863,11 +818,6 @@
           <t>-1658.85億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -885,15 +835,11 @@
           <t>20634口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>19007口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -911,7 +857,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>33.72億</t>
@@ -1016,10 +961,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1141,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1175,6 +1116,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1295,7 +1237,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1303,26 +1245,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>73.59999999999999</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>-4.23</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="7" t="n">
         <v>542230</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>-200178</v>
       </c>
       <c r="H4" t="n">
-        <v>-423563</v>
+        <v>-623741</v>
       </c>
       <c r="I4" t="n">
         <v>4948</v>
       </c>
       <c r="J4" t="n">
-        <v>10872</v>
+        <v>15820</v>
       </c>
       <c r="K4" t="n">
         <v>220371</v>
@@ -1331,11 +1273,14 @@
         <v>14387</v>
       </c>
       <c r="M4" t="n">
-        <v>43522</v>
+        <v>56889</v>
       </c>
       <c r="N4" t="n">
         <v>-4389094</v>
       </c>
+      <c r="O4" t="n">
+        <v>-2.89</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1358,26 +1303,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>871</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>-5.94</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="7" t="n">
         <v>4645</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>-3</v>
       </c>
       <c r="H5" t="n">
-        <v>-1795</v>
+        <v>-1798</v>
       </c>
       <c r="I5" t="n">
         <v>-354</v>
       </c>
       <c r="J5" t="n">
-        <v>-233</v>
+        <v>-587</v>
       </c>
       <c r="K5" t="n">
         <v>365</v>
@@ -1386,11 +1331,14 @@
         <v>2768</v>
       </c>
       <c r="M5" t="n">
-        <v>11314</v>
+        <v>14099</v>
       </c>
       <c r="N5" t="n">
         <v>-78828</v>
       </c>
+      <c r="O5" t="n">
+        <v>-9.84</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1413,26 +1361,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1220</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>-7.58</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="6" t="n">
         <v>23398</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>654</v>
       </c>
       <c r="H6" t="n">
-        <v>-5468</v>
+        <v>-4814</v>
       </c>
       <c r="I6" t="n">
         <v>267</v>
       </c>
       <c r="J6" t="n">
-        <v>1054</v>
+        <v>1322</v>
       </c>
       <c r="K6" t="n">
         <v>4578</v>
@@ -1441,11 +1389,14 @@
         <v>5777</v>
       </c>
       <c r="M6" t="n">
-        <v>22763</v>
+        <v>28775</v>
       </c>
       <c r="N6" t="n">
         <v>-649014</v>
       </c>
+      <c r="O6" t="n">
+        <v>-4.16</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1468,26 +1419,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>1810</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>-4.23</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>94441</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>-37837</v>
       </c>
       <c r="H7" t="n">
-        <v>-69233</v>
+        <v>-107069</v>
       </c>
       <c r="I7" t="n">
         <v>2661</v>
       </c>
       <c r="J7" t="n">
-        <v>5185</v>
+        <v>7847</v>
       </c>
       <c r="K7" t="n">
         <v>8007</v>
@@ -1496,11 +1447,14 @@
         <v>25279</v>
       </c>
       <c r="M7" t="n">
-        <v>92535</v>
+        <v>116408</v>
       </c>
       <c r="N7" t="n">
         <v>-6482931</v>
       </c>
+      <c r="O7" t="n">
+        <v>-3.04</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1523,26 +1477,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1380</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>-5.8</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="7" t="n">
         <v>5813</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>-784</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>-781</v>
       </c>
       <c r="I8" t="n">
         <v>167</v>
       </c>
       <c r="J8" t="n">
-        <v>173</v>
+        <v>340</v>
       </c>
       <c r="K8" t="n">
         <v>284</v>
@@ -1551,11 +1505,14 @@
         <v>1808</v>
       </c>
       <c r="M8" t="n">
-        <v>8108</v>
+        <v>9229</v>
       </c>
       <c r="N8" t="n">
         <v>-140179</v>
       </c>
+      <c r="O8" t="n">
+        <v>4.88</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1578,26 +1535,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>1240</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>-9.82</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="7" t="n">
         <v>3029</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>-231</v>
       </c>
       <c r="H9" t="n">
-        <v>-1773</v>
+        <v>-2004</v>
       </c>
       <c r="I9" t="n">
         <v>40</v>
       </c>
       <c r="J9" t="n">
-        <v>402</v>
+        <v>442</v>
       </c>
       <c r="K9" t="n">
         <v>101</v>
@@ -1606,11 +1563,14 @@
         <v>3283</v>
       </c>
       <c r="M9" t="n">
-        <v>11534</v>
+        <v>14568</v>
       </c>
       <c r="N9" t="n">
         <v>-106287</v>
       </c>
+      <c r="O9" t="n">
+        <v>6.06</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1633,26 +1593,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>2175</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>-7.84</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>3391</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>-327</v>
       </c>
       <c r="H10" t="n">
-        <v>-1387</v>
+        <v>-1714</v>
       </c>
       <c r="I10" t="n">
         <v>173</v>
       </c>
       <c r="J10" t="n">
-        <v>917</v>
+        <v>1090</v>
       </c>
       <c r="K10" t="n">
         <v>194</v>
@@ -1661,11 +1621,14 @@
         <v>1754</v>
       </c>
       <c r="M10" t="n">
-        <v>7315</v>
+        <v>9060</v>
       </c>
       <c r="N10" t="n">
         <v>-89500</v>
       </c>
+      <c r="O10" t="n">
+        <v>2.1</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1688,26 +1651,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="6" t="n">
         <v>1710</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>-9.76</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="6" t="n">
         <v>221</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>29</v>
       </c>
       <c r="H11" t="n">
-        <v>220</v>
+        <v>249</v>
       </c>
       <c r="I11" t="n">
         <v>-1</v>
       </c>
       <c r="J11" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
@@ -1716,11 +1679,14 @@
         <v>4641</v>
       </c>
       <c r="M11" t="n">
-        <v>17440</v>
+        <v>22647</v>
       </c>
       <c r="N11" t="n">
         <v>-19186</v>
       </c>
+      <c r="O11" t="n">
+        <v>-11.88</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1743,26 +1709,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>4980</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>-5.14</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="7" t="n">
         <v>806</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>-206</v>
       </c>
       <c r="H12" t="n">
-        <v>154</v>
+        <v>-52</v>
       </c>
       <c r="I12" t="n">
         <v>73</v>
       </c>
       <c r="J12" t="n">
-        <v>118</v>
+        <v>191</v>
       </c>
       <c r="K12" t="n">
         <v>43</v>
@@ -1771,11 +1737,14 @@
         <v>242</v>
       </c>
       <c r="M12" t="n">
-        <v>1228</v>
+        <v>1484</v>
       </c>
       <c r="N12" t="n">
         <v>-8938</v>
       </c>
+      <c r="O12" t="n">
+        <v>7.04</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1798,26 +1767,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="7" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2730</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>-677</v>
       </c>
       <c r="H13" t="n">
-        <v>-1437</v>
+        <v>-2114</v>
       </c>
       <c r="I13" t="n">
         <v>256</v>
       </c>
       <c r="J13" t="n">
-        <v>1301</v>
+        <v>1557</v>
       </c>
       <c r="K13" t="n">
         <v>-38</v>
@@ -1826,11 +1795,14 @@
         <v>-14</v>
       </c>
       <c r="M13" t="n">
-        <v>-181</v>
+        <v>-195</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1853,20 +1825,20 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="7" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3871</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>20</v>
       </c>
       <c r="H14" t="n">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="I14" t="n">
         <v>-0</v>
@@ -1881,11 +1853,14 @@
         <v>-303</v>
       </c>
       <c r="M14" t="n">
-        <v>-453</v>
+        <v>-756</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1908,20 +1883,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1350</v>
+      <c r="D15" s="6" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>82</v>
       </c>
       <c r="H15" t="n">
-        <v>2467</v>
+        <v>2549</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>307</v>
@@ -1933,11 +1911,14 @@
         <v>-191</v>
       </c>
       <c r="M15" t="n">
-        <v>-138</v>
+        <v>-329</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1960,26 +1941,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="F16" t="n">
-        <v>904</v>
+      <c r="D16" s="6" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>-116</v>
       </c>
       <c r="H16" t="n">
-        <v>333</v>
+        <v>217</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K16" t="n">
         <v>-53</v>
@@ -1988,15 +1969,71 @@
         <v>-4</v>
       </c>
       <c r="M16" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>278</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>-4.47</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>1406</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>-354</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-980</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-149</v>
+      </c>
+      <c r="K17" t="n">
+        <v>14</v>
+      </c>
+      <c r="L17" t="n">
+        <v>6711</v>
+      </c>
+      <c r="M17" t="n">
+        <v>33543</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-22097</v>
+      </c>
+      <c r="O17" t="n">
+        <v>7.55</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260309.xlsx
+++ b/outputs/monitor_xlsx/20260309.xlsx
@@ -1082,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1841,7 +1841,7 @@
         <v>628</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>-2164</v>
@@ -2034,6 +2034,165 @@
       </c>
       <c r="O17" t="n">
         <v>7.55</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1665</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>-5.67</v>
+      </c>
+      <c r="F18" t="n">
+        <v>12529</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>-2272</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-11438</v>
+      </c>
+      <c r="I18" t="n">
+        <v>495</v>
+      </c>
+      <c r="J18" t="n">
+        <v>747</v>
+      </c>
+      <c r="K18" t="n">
+        <v>739</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5669</v>
+      </c>
+      <c r="M18" t="n">
+        <v>29071</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400933</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-6.11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>389</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-9.949999999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>16081</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>-1056</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-4891</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-619</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-1080</v>
+      </c>
+      <c r="K19" t="n">
+        <v>753</v>
+      </c>
+      <c r="L19" t="n">
+        <v>37261</v>
+      </c>
+      <c r="M19" t="n">
+        <v>198046</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-392455</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-11.32</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>423</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="F20" t="n">
+        <v>710</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>176</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2667</v>
+      </c>
+      <c r="I20" t="n">
+        <v>7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>576</v>
+      </c>
+      <c r="K20" t="n">
+        <v>138</v>
+      </c>
+      <c r="L20" t="n">
+        <v>9524</v>
+      </c>
+      <c r="M20" t="n">
+        <v>51575</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-161541</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-10.78</v>
       </c>
     </row>
   </sheetData>
